--- a/NewShopEntry/ChickenStation/CreditManagementOfChickenStation.xlsx
+++ b/NewShopEntry/ChickenStation/CreditManagementOfChickenStation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\shop-main\NewShopEntry\ChickenStation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF4984EE-9152-4F41-99F0-986DA16FC26F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8FDD47D-1C18-479A-BA25-B419BC90D622}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="4" xr2:uid="{11B51453-E16A-4D9E-A0FF-15700BE48989}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="7" xr2:uid="{11B51453-E16A-4D9E-A0FF-15700BE48989}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet7" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet8" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="129">
   <si>
     <t>Date</t>
   </si>
@@ -251,13 +254,178 @@
   </si>
   <si>
     <t>For the Month Baishak,2081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/01/05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/01/07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/01/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/01/14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/01/15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/01/17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/01/21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/01/24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/01/25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/01/31</t>
+  </si>
+  <si>
+    <t>For the Month Jestha,2081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/02/01</t>
+  </si>
+  <si>
+    <t>Balance For Baishak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/02/05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/02/06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/02/11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/02/13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/02/16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/02/19</t>
+  </si>
+  <si>
+    <t>Balance For Jestha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/02/21</t>
+  </si>
+  <si>
+    <t>CASH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/02/27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/02/31</t>
+  </si>
+  <si>
+    <t>RICE</t>
+  </si>
+  <si>
+    <t>For the Month Ashad,2081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/03/02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/03/03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/03/18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/03/19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/03/26</t>
+  </si>
+  <si>
+    <t>Rice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/03/27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/03/29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/03/23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/04/06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/04/07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/04/11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/04/17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/04/21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/04/26</t>
+  </si>
+  <si>
+    <t>For the Month Shrawan,Bhadra,2081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/04/28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/05/01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/05/05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/05/09</t>
+  </si>
+  <si>
+    <t>FONEPAY</t>
+  </si>
+  <si>
+    <t>Cash(FONEPAY)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/05/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/05/15</t>
+  </si>
+  <si>
+    <t>Balance For Ashad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/05/18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/05/23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/05/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balance For Shrawan,Bhadra </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -293,6 +461,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -320,7 +495,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -380,11 +555,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -403,6 +589,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -418,7 +606,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -745,26 +935,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="33.6" x14ac:dyDescent="0.65">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:7" ht="33.6" x14ac:dyDescent="0.65">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="21"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="23"/>
     </row>
     <row r="3" spans="1:7" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A3" s="1" t="s">
@@ -1111,12 +1301,12 @@
       <c r="G18" s="3"/>
     </row>
     <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
       <c r="E19" s="7">
         <f>SUM(E4:E18)</f>
         <v>82050</v>
@@ -1155,26 +1345,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="33.6" x14ac:dyDescent="0.65">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:7" ht="33.6" x14ac:dyDescent="0.65">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="21"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="23"/>
     </row>
     <row r="3" spans="1:7" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A3" s="1" t="s">
@@ -1627,12 +1817,12 @@
       </c>
     </row>
     <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
       <c r="E23" s="7">
         <f>SUM(E4:E22)</f>
         <v>74865</v>
@@ -1672,26 +1862,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="33.6" x14ac:dyDescent="0.65">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:7" ht="33.6" x14ac:dyDescent="0.65">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="21"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="23"/>
     </row>
     <row r="3" spans="1:7" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A3" s="1" t="s">
@@ -2130,12 +2320,12 @@
       <c r="G22" s="15"/>
     </row>
     <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
       <c r="E23" s="7">
         <f>SUM(E4:E22)</f>
         <v>87190</v>
@@ -2175,26 +2365,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="33.6" x14ac:dyDescent="0.65">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:7" ht="33.6" x14ac:dyDescent="0.65">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="21"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="23"/>
     </row>
     <row r="3" spans="1:7" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A3" s="1" t="s">
@@ -2271,12 +2461,12 @@
         <v>2025</v>
       </c>
       <c r="E6" s="4">
-        <f t="shared" ref="E6:E21" si="0">C6*D6</f>
+        <f t="shared" ref="E6:E19" si="0">C6*D6</f>
         <v>4050</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5">
-        <f t="shared" ref="G6:G21" si="1">G5+E6-F6</f>
+        <f t="shared" ref="G6:G19" si="1">G5+E6-F6</f>
         <v>54740</v>
       </c>
     </row>
@@ -2555,7 +2745,7 @@
       </c>
     </row>
     <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="23">
+      <c r="A19" s="18">
         <v>66112</v>
       </c>
       <c r="B19" s="15" t="s">
@@ -2603,12 +2793,12 @@
       <c r="G22" s="15"/>
     </row>
     <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
       <c r="E23" s="7">
         <f>SUM(E4:E22)</f>
         <v>91015</v>
@@ -2647,26 +2837,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="33.6" x14ac:dyDescent="0.65">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:7" ht="33.6" x14ac:dyDescent="0.65">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="21"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="23"/>
     </row>
     <row r="3" spans="1:7" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A3" s="1" t="s">
@@ -2707,200 +2897,300 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
+      <c r="A5" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5">
+        <v>3500</v>
+      </c>
       <c r="E5" s="4">
         <f>C5*D5</f>
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5">
         <f>G4+E5-F5</f>
-        <v>51015</v>
+        <v>54515</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
+      <c r="A6" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5">
+        <v>2100</v>
+      </c>
       <c r="E6" s="4">
-        <f t="shared" ref="E6:E21" si="0">C6*D6</f>
-        <v>0</v>
+        <f t="shared" ref="E6:E17" si="0">C6*D6</f>
+        <v>2100</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5">
-        <f t="shared" ref="G6:G19" si="1">G5+E6-F6</f>
-        <v>51015</v>
+        <f t="shared" ref="G6:G17" si="1">G5+E6-F6</f>
+        <v>56615</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
+      <c r="A7" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>3450</v>
+      </c>
       <c r="E7" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3450</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5">
         <f t="shared" si="1"/>
-        <v>51015</v>
+        <v>60065</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
+      <c r="A8" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5">
+        <v>2025</v>
+      </c>
       <c r="E8" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2025</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5">
         <f t="shared" si="1"/>
-        <v>51015</v>
+        <v>62090</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
+      <c r="A9" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="5">
+        <v>2</v>
+      </c>
+      <c r="D9" s="5">
+        <v>2025</v>
+      </c>
       <c r="E9" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4050</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5">
         <f t="shared" si="1"/>
-        <v>51015</v>
+        <v>66140</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
+      <c r="A10" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F10" s="13"/>
+      <c r="F10" s="13">
+        <v>30000</v>
+      </c>
       <c r="G10" s="5">
         <f t="shared" si="1"/>
-        <v>51015</v>
+        <v>36140</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
+      <c r="A11" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5">
+        <v>3500</v>
+      </c>
       <c r="E11" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5">
         <f t="shared" si="1"/>
-        <v>51015</v>
+        <v>39640</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="A12" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5">
+        <v>2025</v>
+      </c>
       <c r="E12" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2025</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5">
         <f t="shared" si="1"/>
-        <v>51015</v>
+        <v>41665</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+      <c r="A13" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="5">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5">
+        <v>2025</v>
+      </c>
       <c r="E13" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4050</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5">
         <f t="shared" si="1"/>
-        <v>51015</v>
+        <v>45715</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="A14" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="5">
+        <v>2</v>
+      </c>
+      <c r="D14" s="5">
+        <v>2025</v>
+      </c>
       <c r="E14" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4050</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>51015</v>
+        <v>49765</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
+      <c r="A15" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="13">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13">
+        <v>2025</v>
+      </c>
       <c r="E15" s="4">
         <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
+      <c r="F15" s="13">
         <v>0</v>
       </c>
-      <c r="F15" s="13">
-        <v>20000</v>
-      </c>
       <c r="G15" s="5">
         <f t="shared" si="1"/>
-        <v>31015</v>
+        <v>51790</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="11"/>
+      <c r="A16" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="13">
+        <v>1</v>
+      </c>
+      <c r="D16" s="13">
+        <v>2100</v>
+      </c>
+      <c r="E16" s="14">
+        <f t="shared" si="0"/>
+        <v>2100</v>
+      </c>
+      <c r="F16" s="13"/>
       <c r="G16" s="5">
         <f t="shared" si="1"/>
-        <v>31015</v>
+        <v>53890</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
-      <c r="B17" s="15"/>
+      <c r="A17" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
       <c r="E17" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F17" s="15"/>
+      <c r="F17" s="15">
+        <v>25000</v>
+      </c>
       <c r="G17" s="5">
         <f t="shared" si="1"/>
-        <v>31015</v>
+        <v>28890</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
@@ -2908,32 +3198,18 @@
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
-      <c r="E18" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="E18" s="4"/>
       <c r="F18" s="15"/>
-      <c r="G18" s="5">
-        <f t="shared" si="1"/>
-        <v>31015</v>
-      </c>
+      <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="23"/>
+      <c r="A19" s="18"/>
       <c r="B19" s="15"/>
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
-      <c r="E19" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F19" s="15">
-        <v>20000</v>
-      </c>
-      <c r="G19" s="5">
-        <f t="shared" si="1"/>
-        <v>11015</v>
-      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
@@ -2963,23 +3239,23 @@
       <c r="G22" s="15"/>
     </row>
     <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
+      <c r="A23" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
       <c r="E23" s="7">
         <f>SUM(E4:E22)</f>
-        <v>51015</v>
+        <v>83890</v>
       </c>
       <c r="F23" s="8">
         <f>SUM(F4:F22)</f>
-        <v>40000</v>
+        <v>55000</v>
       </c>
       <c r="G23" s="9">
         <f>E23-F23</f>
-        <v>11015</v>
+        <v>28890</v>
       </c>
     </row>
   </sheetData>
@@ -2990,4 +3266,1325 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87DD37A2-4887-4B74-80E0-6CAB9C9A2B3D}">
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="33.6" x14ac:dyDescent="0.65">
+      <c r="A1" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+    </row>
+    <row r="2" spans="1:7" ht="33.6" x14ac:dyDescent="0.65">
+      <c r="A2" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="23"/>
+    </row>
+    <row r="3" spans="1:7" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="5">
+        <v>28890</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="5">
+        <v>28890</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="5">
+        <v>2</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E5" s="4">
+        <f>C5*D5</f>
+        <v>4050</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5">
+        <f>G4+E5-F5</f>
+        <v>32940</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5">
+        <v>2100</v>
+      </c>
+      <c r="E6" s="4">
+        <f t="shared" ref="E6:E17" si="0">C6*D6</f>
+        <v>2100</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5">
+        <f t="shared" ref="G6:G17" si="1">G5+E6-F6</f>
+        <v>35040</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="5">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5">
+        <v>2020</v>
+      </c>
+      <c r="E7" s="4">
+        <f t="shared" si="0"/>
+        <v>4040</v>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5">
+        <f t="shared" si="1"/>
+        <v>39080</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="5">
+        <v>2</v>
+      </c>
+      <c r="D8" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E8" s="4">
+        <f t="shared" si="0"/>
+        <v>4050</v>
+      </c>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5">
+        <f t="shared" si="1"/>
+        <v>43130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5">
+        <v>3400</v>
+      </c>
+      <c r="E9" s="4">
+        <f t="shared" si="0"/>
+        <v>3400</v>
+      </c>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5">
+        <f t="shared" si="1"/>
+        <v>46530</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E10" s="4">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
+      <c r="F10" s="13">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <f t="shared" si="1"/>
+        <v>48555</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E11" s="4">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5">
+        <f t="shared" si="1"/>
+        <v>50580</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5">
+        <v>2100</v>
+      </c>
+      <c r="E12" s="4">
+        <f t="shared" si="0"/>
+        <v>2100</v>
+      </c>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5">
+        <f t="shared" si="1"/>
+        <v>52680</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="5">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E13" s="4">
+        <f t="shared" si="0"/>
+        <v>4050</v>
+      </c>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5">
+        <f t="shared" si="1"/>
+        <v>56730</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>25000</v>
+      </c>
+      <c r="G14" s="5">
+        <f t="shared" si="1"/>
+        <v>31730</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="13">
+        <v>2</v>
+      </c>
+      <c r="D15" s="13">
+        <v>2025</v>
+      </c>
+      <c r="E15" s="4">
+        <f t="shared" si="0"/>
+        <v>4050</v>
+      </c>
+      <c r="F15" s="13">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <f t="shared" si="1"/>
+        <v>35780</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="13">
+        <v>1</v>
+      </c>
+      <c r="D16" s="13">
+        <v>2100</v>
+      </c>
+      <c r="E16" s="14">
+        <f t="shared" si="0"/>
+        <v>2100</v>
+      </c>
+      <c r="F16" s="13"/>
+      <c r="G16" s="5">
+        <f t="shared" si="1"/>
+        <v>37880</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="5"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="15"/>
+      <c r="G17" s="5">
+        <f t="shared" si="1"/>
+        <v>37880</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="5"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="5"/>
+    </row>
+    <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="18"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="5"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="5"/>
+    </row>
+    <row r="21" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="5"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="5"/>
+    </row>
+    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="15"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="15"/>
+    </row>
+    <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="7">
+        <f>SUM(E4:E22)</f>
+        <v>62880</v>
+      </c>
+      <c r="F23" s="8">
+        <f>SUM(F4:F22)</f>
+        <v>25000</v>
+      </c>
+      <c r="G23" s="9">
+        <f>E23-F23</f>
+        <v>37880</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A23:D23"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="75" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{649FD9E5-8C20-43A0-AD99-185CC898F645}">
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="33.6" x14ac:dyDescent="0.65">
+      <c r="A1" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+    </row>
+    <row r="2" spans="1:7" ht="33.6" x14ac:dyDescent="0.65">
+      <c r="A2" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="23"/>
+    </row>
+    <row r="3" spans="1:7" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="5">
+        <v>37880</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="5">
+        <v>37880</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E5" s="4">
+        <f>C5*D5</f>
+        <v>2025</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5">
+        <f>G4+E5-F5</f>
+        <v>39905</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="5">
+        <v>3</v>
+      </c>
+      <c r="D6" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E6" s="4">
+        <f t="shared" ref="E6:E8" si="0">C6*D6</f>
+        <v>6075</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5">
+        <f t="shared" ref="G6:G9" si="1">G5+E6-F6</f>
+        <v>45980</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="5">
+        <v>25000</v>
+      </c>
+      <c r="G7" s="5">
+        <f t="shared" si="1"/>
+        <v>20980</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="5">
+        <v>2</v>
+      </c>
+      <c r="D8" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E8" s="4">
+        <f t="shared" si="0"/>
+        <v>4050</v>
+      </c>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5">
+        <f t="shared" si="1"/>
+        <v>25030</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="F9">
+        <v>10000</v>
+      </c>
+      <c r="G9" s="5">
+        <f t="shared" si="1"/>
+        <v>15030</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5">
+        <v>2100</v>
+      </c>
+      <c r="E10" s="4">
+        <f>C10*D10</f>
+        <v>2100</v>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5">
+        <f>G9+E10-F10</f>
+        <v>17130</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E11" s="4">
+        <f>C11*D11</f>
+        <v>2025</v>
+      </c>
+      <c r="F11" s="13">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <f>G10+E11-F11</f>
+        <v>19155</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E12" s="4">
+        <f>C12*D12</f>
+        <v>2025</v>
+      </c>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5">
+        <f>G11+E12-F12</f>
+        <v>21180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="5">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E13" s="4">
+        <f>C13*D13</f>
+        <v>4050</v>
+      </c>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5">
+        <f>G12+E13-F13</f>
+        <v>25230</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+    </row>
+    <row r="15" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="5"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="5"/>
+    </row>
+    <row r="16" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="5"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="5"/>
+    </row>
+    <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="5"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="5"/>
+    </row>
+    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="5"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="5"/>
+    </row>
+    <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="18"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="5"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="5"/>
+    </row>
+    <row r="21" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="5"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="5"/>
+    </row>
+    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="15"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="15"/>
+    </row>
+    <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="7">
+        <f>SUM(E4:E22)</f>
+        <v>60230</v>
+      </c>
+      <c r="F23" s="8">
+        <f>SUM(F4:F22)</f>
+        <v>35000</v>
+      </c>
+      <c r="G23" s="9">
+        <f>E23-F23</f>
+        <v>25230</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A23:D23"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F95DC35-1328-4FF7-8BC2-1C3BA9E37BF4}">
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="33.6" x14ac:dyDescent="0.65">
+      <c r="A1" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+    </row>
+    <row r="2" spans="1:7" ht="33.6" x14ac:dyDescent="0.65">
+      <c r="A2" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="23"/>
+    </row>
+    <row r="3" spans="1:7" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="5">
+        <v>25230</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="5">
+        <f>E4</f>
+        <v>25230</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E5" s="4">
+        <f>C5*D5</f>
+        <v>2025</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5">
+        <f>G4+E5-F5</f>
+        <v>27255</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E6" s="4">
+        <f t="shared" ref="E6:E21" si="0">C6*D6</f>
+        <v>2025</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5">
+        <f t="shared" ref="G6" si="1">G5+E6-F6</f>
+        <v>29280</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="5">
+        <v>15000</v>
+      </c>
+      <c r="G7" s="5">
+        <f>G6+E7-F7</f>
+        <v>14280</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="5">
+        <v>2</v>
+      </c>
+      <c r="D8" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E8" s="4">
+        <f t="shared" si="0"/>
+        <v>4050</v>
+      </c>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5">
+        <f>G7+E8-F8</f>
+        <v>18330</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="5">
+        <v>2</v>
+      </c>
+      <c r="D9" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E9" s="4">
+        <f t="shared" si="0"/>
+        <v>4050</v>
+      </c>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5">
+        <f>G8+E9-F9</f>
+        <v>22380</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2</v>
+      </c>
+      <c r="D10" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E10" s="4">
+        <f t="shared" si="0"/>
+        <v>4050</v>
+      </c>
+      <c r="F10" s="13"/>
+      <c r="G10" s="5">
+        <f t="shared" ref="G10:G22" si="2">G9+E10-F10</f>
+        <v>26430</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E11" s="4">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5">
+        <f t="shared" si="2"/>
+        <v>28455</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="5">
+        <v>2</v>
+      </c>
+      <c r="D12" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E12" s="4">
+        <f t="shared" si="0"/>
+        <v>4050</v>
+      </c>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5">
+        <f t="shared" si="2"/>
+        <v>32505</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>10000</v>
+      </c>
+      <c r="G13" s="5">
+        <f t="shared" si="2"/>
+        <v>22505</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="5">
+        <v>2</v>
+      </c>
+      <c r="D14" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E14" s="4">
+        <f t="shared" si="0"/>
+        <v>4050</v>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5">
+        <f t="shared" si="2"/>
+        <v>26555</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="13">
+        <v>2</v>
+      </c>
+      <c r="D15" s="13">
+        <v>2025</v>
+      </c>
+      <c r="E15" s="4">
+        <f t="shared" si="0"/>
+        <v>4050</v>
+      </c>
+      <c r="F15" s="13"/>
+      <c r="G15" s="5">
+        <f t="shared" si="2"/>
+        <v>30605</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="13">
+        <v>15000</v>
+      </c>
+      <c r="G16" s="5">
+        <f t="shared" si="2"/>
+        <v>15605</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="15">
+        <v>2</v>
+      </c>
+      <c r="D17" s="15">
+        <v>2025</v>
+      </c>
+      <c r="E17" s="4">
+        <f t="shared" si="0"/>
+        <v>4050</v>
+      </c>
+      <c r="F17" s="15"/>
+      <c r="G17" s="5">
+        <f t="shared" si="2"/>
+        <v>19655</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="15">
+        <v>2</v>
+      </c>
+      <c r="D18" s="15">
+        <v>2025</v>
+      </c>
+      <c r="E18" s="4">
+        <f t="shared" si="0"/>
+        <v>4050</v>
+      </c>
+      <c r="F18" s="15"/>
+      <c r="G18" s="5">
+        <f t="shared" si="2"/>
+        <v>23705</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="15">
+        <v>2</v>
+      </c>
+      <c r="D19" s="15">
+        <v>2025</v>
+      </c>
+      <c r="E19" s="4">
+        <f t="shared" si="0"/>
+        <v>4050</v>
+      </c>
+      <c r="F19" s="15"/>
+      <c r="G19" s="5">
+        <f t="shared" si="2"/>
+        <v>27755</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="15">
+        <v>1</v>
+      </c>
+      <c r="D20" s="15">
+        <v>2025</v>
+      </c>
+      <c r="E20" s="4">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
+      <c r="F20" s="15"/>
+      <c r="G20" s="5">
+        <f t="shared" si="2"/>
+        <v>29780</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="15">
+        <v>2</v>
+      </c>
+      <c r="D21" s="15">
+        <v>2025</v>
+      </c>
+      <c r="E21" s="4">
+        <f t="shared" si="0"/>
+        <v>4050</v>
+      </c>
+      <c r="F21" s="15"/>
+      <c r="G21" s="5">
+        <f t="shared" si="2"/>
+        <v>33830</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="15"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="7">
+        <f>SUM(E4:E22)</f>
+        <v>73830</v>
+      </c>
+      <c r="F23" s="8">
+        <f>SUM(F4:F22)</f>
+        <v>40000</v>
+      </c>
+      <c r="G23" s="9">
+        <f>E23-F23</f>
+        <v>33830</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A23:D23"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/NewShopEntry/ChickenStation/CreditManagementOfChickenStation.xlsx
+++ b/NewShopEntry/ChickenStation/CreditManagementOfChickenStation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\shop-main\NewShopEntry\ChickenStation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8FDD47D-1C18-479A-BA25-B419BC90D622}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{182B70CF-EBF4-4D62-8E85-B77464E6213B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="7" xr2:uid="{11B51453-E16A-4D9E-A0FF-15700BE48989}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="8" xr2:uid="{11B51453-E16A-4D9E-A0FF-15700BE48989}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,8 @@
     <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
     <sheet name="Sheet7" sheetId="7" r:id="rId7"/>
     <sheet name="Sheet8" sheetId="8" r:id="rId8"/>
+    <sheet name="Sheet9" sheetId="12" r:id="rId9"/>
+    <sheet name="Sheet10" sheetId="13" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="146">
   <si>
     <t>Date</t>
   </si>
@@ -419,6 +421,57 @@
   </si>
   <si>
     <t xml:space="preserve">Balance For Shrawan,Bhadra </t>
+  </si>
+  <si>
+    <t>For the Month Ashoj,2081</t>
+  </si>
+  <si>
+    <t>For the Month Kartik,2081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2081/05/29</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2081/06/03</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2081/06/06</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2081/06/07</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2081/06/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2081/06/17</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2081/06/18</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2081/06/22</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2081/06/23</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2081/07/02</t>
+  </si>
+  <si>
+    <t>Esewa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2081/06/20</t>
+  </si>
+  <si>
+    <t>25th dec 2024</t>
+  </si>
+  <si>
+    <t>27th jan 2025</t>
+  </si>
+  <si>
+    <t>S</t>
   </si>
 </sst>
 </file>
@@ -1331,6 +1384,379 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51C36794-24A9-4D9F-900A-59E9F04A5E08}">
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="33.6" x14ac:dyDescent="0.65">
+      <c r="A1" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+    </row>
+    <row r="2" spans="1:7" ht="33.6" x14ac:dyDescent="0.65">
+      <c r="A2" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="23"/>
+    </row>
+    <row r="3" spans="1:7" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="5">
+        <f>E4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="4">
+        <f>C5*D5</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5">
+        <f>G4+E5-F5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="4">
+        <f t="shared" ref="E6:E21" si="0">C6*D6</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5">
+        <f t="shared" ref="G6" si="1">G5+E6-F6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="5">
+        <v>15000</v>
+      </c>
+      <c r="G7" s="5">
+        <f>G6+E7-F7</f>
+        <v>-15000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5">
+        <f>G7+E8-F8</f>
+        <v>-15000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5">
+        <f>G8+E9-F9</f>
+        <v>-15000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="13"/>
+      <c r="G10" s="5">
+        <f t="shared" ref="G10:G21" si="2">G9+E10-F10</f>
+        <v>-15000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5">
+        <f t="shared" si="2"/>
+        <v>-15000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5">
+        <f t="shared" si="2"/>
+        <v>-15000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>10000</v>
+      </c>
+      <c r="G13" s="5">
+        <f t="shared" si="2"/>
+        <v>-25000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5">
+        <f t="shared" si="2"/>
+        <v>-25000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="5"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="13"/>
+      <c r="G15" s="5">
+        <f t="shared" si="2"/>
+        <v>-25000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="5"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="13">
+        <v>15000</v>
+      </c>
+      <c r="G16" s="5">
+        <f t="shared" si="2"/>
+        <v>-40000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="5"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="15"/>
+      <c r="G17" s="5">
+        <f t="shared" si="2"/>
+        <v>-40000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="5"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="15"/>
+      <c r="G18" s="5">
+        <f t="shared" si="2"/>
+        <v>-40000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="5"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="15"/>
+      <c r="G19" s="5">
+        <f t="shared" si="2"/>
+        <v>-40000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="5"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="15"/>
+      <c r="G20" s="5">
+        <f t="shared" si="2"/>
+        <v>-40000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="5"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="15"/>
+      <c r="G21" s="5">
+        <f t="shared" si="2"/>
+        <v>-40000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="15"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="7">
+        <f>SUM(E4:E22)</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="8">
+        <f>SUM(F4:F22)</f>
+        <v>40000</v>
+      </c>
+      <c r="G23" s="9">
+        <f>E23-F23</f>
+        <v>-40000</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A23:D23"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F60CDA9-A6E9-48B4-90EA-9BDA2EB4F082}">
   <dimension ref="A1:G23"/>
@@ -4204,7 +4630,7 @@
         <v>2025</v>
       </c>
       <c r="E6" s="4">
-        <f t="shared" ref="E6:E21" si="0">C6*D6</f>
+        <f t="shared" ref="E6:E22" si="0">C6*D6</f>
         <v>2025</v>
       </c>
       <c r="F6" s="5"/>
@@ -4550,13 +4976,27 @@
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="15"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="4"/>
+      <c r="A22" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="17">
+        <v>2</v>
+      </c>
+      <c r="D22" s="17">
+        <v>2025</v>
+      </c>
+      <c r="E22" s="4">
+        <f t="shared" si="0"/>
+        <v>4050</v>
+      </c>
       <c r="F22" s="17"/>
-      <c r="G22" s="5"/>
+      <c r="G22" s="5">
+        <f t="shared" si="2"/>
+        <v>37880</v>
+      </c>
     </row>
     <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="25" t="s">
@@ -4567,7 +5007,7 @@
       <c r="D23" s="25"/>
       <c r="E23" s="7">
         <f>SUM(E4:E22)</f>
-        <v>73830</v>
+        <v>77880</v>
       </c>
       <c r="F23" s="8">
         <f>SUM(F4:F22)</f>
@@ -4575,7 +5015,7 @@
       </c>
       <c r="G23" s="9">
         <f>E23-F23</f>
-        <v>33830</v>
+        <v>37880</v>
       </c>
     </row>
   </sheetData>
@@ -4587,4 +5027,445 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43567CE6-96CB-44C4-92BE-B207D236CA95}">
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.6640625" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="33.6" x14ac:dyDescent="0.65">
+      <c r="A1" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+    </row>
+    <row r="2" spans="1:7" ht="33.6" x14ac:dyDescent="0.65">
+      <c r="A2" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="23"/>
+    </row>
+    <row r="3" spans="1:7" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="5">
+        <v>37880</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="5">
+        <f>E4</f>
+        <v>37880</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="5">
+        <v>2</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E5" s="4">
+        <f>C5*D5</f>
+        <v>4050</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5">
+        <f>G4+E5-F5</f>
+        <v>41930</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E6" s="4">
+        <f>C6*D6</f>
+        <v>2025</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5">
+        <f t="shared" ref="G6:G15" si="0">G5+E6-F6</f>
+        <v>43955</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="F7">
+        <v>20000</v>
+      </c>
+      <c r="G7" s="5">
+        <f t="shared" si="0"/>
+        <v>23955</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="5">
+        <v>2</v>
+      </c>
+      <c r="D8" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E8" s="4">
+        <f t="shared" ref="E8:E15" si="1">C8*D8</f>
+        <v>4050</v>
+      </c>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5">
+        <f t="shared" si="0"/>
+        <v>28005</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="5">
+        <v>2</v>
+      </c>
+      <c r="D9" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E9" s="4">
+        <f t="shared" si="1"/>
+        <v>4050</v>
+      </c>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5">
+        <f t="shared" si="0"/>
+        <v>32055</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E10" s="4">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5">
+        <f t="shared" si="0"/>
+        <v>34080</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E11" s="4">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="F11" s="13"/>
+      <c r="G11" s="5">
+        <f t="shared" si="0"/>
+        <v>36105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="13">
+        <v>20000</v>
+      </c>
+      <c r="G12" s="5">
+        <f t="shared" si="0"/>
+        <v>16105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E13" s="4">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5">
+        <f t="shared" si="0"/>
+        <v>18130</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="5">
+        <v>2</v>
+      </c>
+      <c r="D14" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E14" s="4">
+        <f t="shared" si="1"/>
+        <v>4050</v>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5">
+        <f t="shared" si="0"/>
+        <v>22180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="5">
+        <v>2</v>
+      </c>
+      <c r="D15" s="5">
+        <v>2025</v>
+      </c>
+      <c r="E15" s="4">
+        <f t="shared" si="1"/>
+        <v>4050</v>
+      </c>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5">
+        <f t="shared" si="0"/>
+        <v>26230</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="5">
+        <v>10000</v>
+      </c>
+      <c r="G16" s="5"/>
+    </row>
+    <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="13">
+        <v>10000</v>
+      </c>
+      <c r="G17" s="5"/>
+    </row>
+    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="5"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="5"/>
+    </row>
+    <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="5"/>
+      <c r="B19" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="5"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="5"/>
+    </row>
+    <row r="21" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="5"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="5"/>
+    </row>
+    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="5"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="5"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="5"/>
+    </row>
+    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="15"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="5"/>
+    </row>
+    <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="7">
+        <f>SUM(E4:E24)</f>
+        <v>66230</v>
+      </c>
+      <c r="F25" s="8">
+        <f>SUM(F4:F24)</f>
+        <v>60000</v>
+      </c>
+      <c r="G25" s="9">
+        <f>E25-F25</f>
+        <v>6230</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A25:D25"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>